--- a/sample_templates/工单明细.xlsx
+++ b/sample_templates/工单明细.xlsx
@@ -455,18 +455,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -479,7 +480,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>按工单填写明细；示例行（工单编号以"示例-"开头）上传时自动跳过。时间格式如 2026-07-05 18:00。完成状态可填：未开工/部分完成/已完成（也可留空）。</t>
+          <t>按工单填写明细；示例行（工单编号以"示例-"开头）上传时自动跳过。类别如：染色纤维/纱线/坯布/面料等。时间格式如 2026-07-05 18:00。完成状态可填：未开工/部分完成/已完成（也可留空）。</t>
         </is>
       </c>
     </row>
@@ -501,30 +502,35 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
+          <t>类别</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
           <t>计划完工时间</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>实际完工时间</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>完成状态</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>计划数量</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>投料数量</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>入库数量</t>
         </is>
@@ -548,30 +554,35 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
+          <t>染色纤维</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
           <t>2026-07-05 18:00</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>2026-07-05 17:30</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>已完成</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="H4" s="5" t="inlineStr">
         <is>
           <t>5000</t>
         </is>
       </c>
-      <c r="H4" s="5" t="inlineStr">
+      <c r="I4" s="5" t="inlineStr">
         <is>
           <t>5020</t>
         </is>
       </c>
-      <c r="I4" s="5" t="inlineStr">
+      <c r="J4" s="5" t="inlineStr">
         <is>
           <t>4980</t>
         </is>
@@ -595,30 +606,35 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
+          <t>纱线</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
           <t>2026-07-08 18:00</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>2026-07-08 16:00</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>已完成</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="H5" s="5" t="inlineStr">
         <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="H5" s="5" t="inlineStr">
+      <c r="I5" s="5" t="inlineStr">
         <is>
           <t>1010</t>
         </is>
       </c>
-      <c r="I5" s="5" t="inlineStr">
+      <c r="J5" s="5" t="inlineStr">
         <is>
           <t>998</t>
         </is>
@@ -634,6 +650,7 @@
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr"/>
@@ -645,6 +662,7 @@
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr"/>
@@ -656,6 +674,7 @@
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr"/>
@@ -667,6 +686,7 @@
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr"/>
@@ -678,11 +698,12 @@
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A2:J2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/sample_templates/工单明细.xlsx
+++ b/sample_templates/工单明细.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -480,7 +480,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>按工单填写明细；示例行（工单编号以"示例-"开头）上传时自动跳过。类别如：染色纤维/纱线/坯布/面料等。时间格式如 2026-07-05 18:00。完成状态可填：未开工/部分完成/已完成（也可留空）。</t>
+          <t>按工单填写明细；示例行（工单编号以"示例-"开头）上传时自动跳过。时间格式如 2026-07-05 18:00。完成状态可填：未开工/部分完成/已完成（也可留空）。</t>
         </is>
       </c>
     </row>
@@ -502,35 +502,30 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>类别</t>
+          <t>计划完工时间</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>计划完工时间</t>
+          <t>实际完工时间</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>实际完工时间</t>
+          <t>完成状态</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>完成状态</t>
+          <t>计划数量</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>计划数量</t>
+          <t>投料数量</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>投料数量</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>入库数量</t>
         </is>
@@ -554,35 +549,30 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>染色纤维</t>
+          <t>2026-07-05 18:00</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>2026-07-05 18:00</t>
+          <t>2026-07-05 17:30</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>2026-07-05 17:30</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
           <t>已完成</t>
         </is>
       </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
       <c r="H4" s="5" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>5020</t>
         </is>
       </c>
       <c r="I4" s="5" t="inlineStr">
-        <is>
-          <t>5020</t>
-        </is>
-      </c>
-      <c r="J4" s="5" t="inlineStr">
         <is>
           <t>4980</t>
         </is>
@@ -606,100 +596,40 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>纱线</t>
+          <t>2026-07-08 18:00</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>2026-07-08 18:00</t>
+          <t>2026-07-08 16:00</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>2026-07-08 16:00</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
           <t>已完成</t>
         </is>
       </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1010</t>
         </is>
       </c>
       <c r="I5" s="5" t="inlineStr">
         <is>
-          <t>1010</t>
-        </is>
-      </c>
-      <c r="J5" s="5" t="inlineStr">
-        <is>
           <t>998</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr"/>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr"/>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr"/>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr"/>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr"/>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-    </row>
+    <row r="6"/>
+    <row r="7"/>
+    <row r="8"/>
+    <row r="9"/>
+    <row r="10"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:J1"/>
